--- a/output/pdf_financials_xlsx/DHT.U.xlsx
+++ b/output/pdf_financials_xlsx/DHT.U.xlsx
@@ -1209,15 +1209,11 @@
       <c r="C23" s="3" t="n">
         <v>21.563</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D23" s="3" t="n">
+        <v>10.953</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>91.496</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -1618,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>4.235</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>3.311</v>
       </c>
     </row>
     <row r="36">
@@ -1645,10 +1641,10 @@
         <v>62.835</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>36.502</v>
+        <v>40.737</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>42.432</v>
+        <v>45.743</v>
       </c>
     </row>
     <row r="37">
@@ -1717,10 +1713,10 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0</v>
+        <v>49.606</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0</v>
+        <v>49.897</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>0</v>
@@ -1771,10 +1767,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>49.606</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>49.897</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0</v>
@@ -2540,16 +2536,16 @@
         <v>5.321</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>34.571</v>
+        <v>43.921</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>145.478</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>320.753</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0</v>
+        <v>376.064</v>
       </c>
     </row>
     <row r="70">
@@ -2594,16 +2590,16 @@
         <v>5.321</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>34.571</v>
+        <v>43.921</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>145.478</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>320.753</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>376.064</v>
       </c>
     </row>
     <row r="72">
@@ -2753,10 +2749,10 @@
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>0</v>
+        <v>38.6</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0</v>
+        <v>210.417</v>
       </c>
       <c r="E77" s="3" t="n">
         <v>0</v>
@@ -2807,10 +2803,10 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>38.6</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>210.417</v>
       </c>
       <c r="E79" s="3" t="n">
         <v>0</v>
@@ -2834,25 +2830,19 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.01404013351451904</v>
+        <v>0.1158911302558149</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.09130308472427635</v>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.6717145573631946</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.2599218508519758</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.6080268268594642</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.8574581604268321</v>
       </c>
     </row>
     <row r="81">
@@ -2975,7 +2965,7 @@
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>38.737</v>
+        <v>0.137</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>0.296</v>
@@ -3335,15 +3325,11 @@
       <c r="C99" s="3" t="n">
         <v>21.563</v>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>10.953</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>91.496</v>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
@@ -4696,7 +4682,11 @@
           <t>Investment in marketable securities note 16</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4972,7 +4962,11 @@
           <t>Current portion of credit facility note 8</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5130,7 +5124,11 @@
           <t>Credit facility note 8</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -5730,7 +5728,11 @@
           <t>Unrealized gain (loss) on marketable securities note 16</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5774,7 +5776,11 @@
           <t>Realized gain (loss) on marketable securities note 16</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -6884,7 +6890,11 @@
           <t>Investment in marketable securities note 15</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -7050,7 +7060,11 @@
           <t>Current portion of credit facility note 9</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -7174,7 +7188,11 @@
           <t>Credit facility note 9</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -7838,7 +7856,11 @@
           <t>Unrealized loss on marketable securities note 15</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -8704,7 +8726,11 @@
           <t>Current portion of credit facility note 9 48,750</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -8876,7 +8902,11 @@
           <t>Credit facility note 9 96,728</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -9888,7 +9918,11 @@
           <t>Loan receivable note 7</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LoansReceivable</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -10060,7 +10094,11 @@
           <t>Long-term debt note 8</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LongTermDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -10900,7 +10938,11 @@
           <t>Loan receivable note 8</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LoansReceivable</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -11116,7 +11158,11 @@
           <t>Long-term debt note 9</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LongTermDebt</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -14866,7 +14912,11 @@
           <t>Net earnings note 2 $</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -16142,7 +16192,11 @@
           <t>Cash interest paid note 8</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -17282,7 +17336,11 @@
           <t>Cash interest paid note 9</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DHT.U.xlsx
+++ b/output/pdf_financials_xlsx/DHT.U.xlsx
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>4.745</v>
       </c>
     </row>
     <row r="116">
@@ -13384,7 +13384,11 @@
           <t>Purchase of marketable securities note 6</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -13430,7 +13434,11 @@
           <t>Proceeds from sale of marketable securities note 16</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
